--- a/informes_data/Euroleague/2025-26/Regular_Season/raw/boxscore_full_analysis_45_EL.xlsx
+++ b/informes_data/Euroleague/2025-26/Regular_Season/raw/boxscore_full_analysis_45_EL.xlsx
@@ -662,10 +662,10 @@
         </is>
       </c>
       <c r="J2" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="K2" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="L2" t="n">
         <v>0</v>
@@ -745,12 +745,12 @@
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>1.09</t>
         </is>
       </c>
       <c r="AG2" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>1.00</t>
         </is>
       </c>
       <c r="AH2" t="inlineStr">
@@ -821,13 +821,13 @@
         </is>
       </c>
       <c r="J3" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="K3" t="n">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="L3" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="M3" t="n">
         <v>9</v>
@@ -904,17 +904,17 @@
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>0.89</t>
         </is>
       </c>
       <c r="AG3" t="inlineStr">
         <is>
-          <t>0.18</t>
+          <t>0.91</t>
         </is>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
-          <t>2.00</t>
+          <t>1.33</t>
         </is>
       </c>
       <c r="AI3" t="inlineStr">
@@ -1335,10 +1335,10 @@
         <v>21</v>
       </c>
       <c r="T17" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="U17" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="V17" t="n">
         <v>0</v>
@@ -1531,7 +1531,7 @@
         <v>2</v>
       </c>
       <c r="T18" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="U18" t="n">
         <v>0</v>
@@ -1923,10 +1923,10 @@
         <v>13</v>
       </c>
       <c r="T20" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="U20" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="V20" t="n">
         <v>0</v>
@@ -2318,7 +2318,7 @@
         <v>0</v>
       </c>
       <c r="U22" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="V22" t="n">
         <v>0</v>
@@ -2511,7 +2511,7 @@
         <v>1</v>
       </c>
       <c r="T23" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="U23" t="n">
         <v>0</v>
@@ -2903,10 +2903,10 @@
         <v>10</v>
       </c>
       <c r="T25" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="U25" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="V25" t="n">
         <v>0</v>
@@ -3494,7 +3494,7 @@
         <v>0</v>
       </c>
       <c r="U28" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="V28" t="n">
         <v>0</v>
@@ -3827,10 +3827,10 @@
         <v>88</v>
       </c>
       <c r="T30" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="U30" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="V30" t="n">
         <v>0</v>
@@ -4298,10 +4298,10 @@
         <v>0</v>
       </c>
       <c r="V35" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="W35" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="X35" t="n">
         <v>4</v>
@@ -4488,7 +4488,7 @@
         <v>5</v>
       </c>
       <c r="T36" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="U36" t="n">
         <v>0</v>
@@ -4687,7 +4687,7 @@
         <v>0</v>
       </c>
       <c r="U37" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="V37" t="n">
         <v>0</v>
@@ -4883,13 +4883,13 @@
         <v>0</v>
       </c>
       <c r="U38" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="V38" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="W38" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X38" t="n">
         <v>5</v>
@@ -5076,10 +5076,10 @@
         <v>18</v>
       </c>
       <c r="T39" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U39" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V39" t="n">
         <v>0</v>
@@ -5468,16 +5468,16 @@
         <v>18</v>
       </c>
       <c r="T41" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="U41" t="n">
         <v>0</v>
       </c>
       <c r="V41" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="W41" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="X41" t="n">
         <v>3</v>
@@ -6448,7 +6448,7 @@
         <v>21</v>
       </c>
       <c r="T46" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="U46" t="n">
         <v>2</v>
@@ -6784,16 +6784,16 @@
         <v>121</v>
       </c>
       <c r="T48" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="U48" t="n">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="V48" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="W48" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="X48" t="n">
         <v>32</v>

--- a/informes_data/Euroleague/2025-26/Regular_Season/raw/boxscore_full_analysis_45_EL.xlsx
+++ b/informes_data/Euroleague/2025-26/Regular_Season/raw/boxscore_full_analysis_45_EL.xlsx
@@ -674,10 +674,10 @@
         <v>9</v>
       </c>
       <c r="N2" t="n">
-        <v>25</v>
+        <v>11</v>
       </c>
       <c r="O2" t="n">
-        <v>34</v>
+        <v>20</v>
       </c>
       <c r="P2" t="n">
         <v>6</v>
@@ -695,17 +695,17 @@
         <v>2</v>
       </c>
       <c r="U2" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="V2" t="n">
         <v>9</v>
       </c>
       <c r="W2" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="X2" t="inlineStr">
         <is>
-          <t>73.53</t>
+          <t>55.00</t>
         </is>
       </c>
       <c r="Y2" t="inlineStr">
@@ -720,17 +720,17 @@
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>33.33</t>
+          <t>28.57</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>50.00</t>
+          <t>52.94</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>1.47</t>
+          <t>1.10</t>
         </is>
       </c>
       <c r="AD2" t="inlineStr">
@@ -833,10 +833,10 @@
         <v>9</v>
       </c>
       <c r="N3" t="n">
-        <v>32</v>
+        <v>14</v>
       </c>
       <c r="O3" t="n">
-        <v>36</v>
+        <v>18</v>
       </c>
       <c r="P3" t="n">
         <v>9</v>
@@ -854,17 +854,17 @@
         <v>3</v>
       </c>
       <c r="U3" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="V3" t="n">
         <v>6</v>
       </c>
       <c r="W3" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="X3" t="inlineStr">
         <is>
-          <t>88.89</t>
+          <t>77.78</t>
         </is>
       </c>
       <c r="Y3" t="inlineStr">
@@ -879,17 +879,17 @@
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>33.33</t>
+          <t>30.00</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>33.33</t>
+          <t>35.29</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>1.78</t>
+          <t>1.56</t>
         </is>
       </c>
       <c r="AD3" t="inlineStr">
@@ -1347,14 +1347,14 @@
         <v>0</v>
       </c>
       <c r="X17" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="Y17" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>66.7%</t>
+          <t>33.3%</t>
         </is>
       </c>
       <c r="AA17" t="n">
@@ -1775,7 +1775,7 @@
         <v>0</v>
       </c>
       <c r="AH19" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AI19" t="inlineStr">
         <is>
@@ -1786,7 +1786,7 @@
         <v>0</v>
       </c>
       <c r="AK19" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AL19" t="inlineStr">
         <is>
@@ -1935,14 +1935,14 @@
         <v>0</v>
       </c>
       <c r="X20" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="Y20" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>80.0%</t>
+          <t>50.0%</t>
         </is>
       </c>
       <c r="AA20" t="n">
@@ -2523,14 +2523,14 @@
         <v>0</v>
       </c>
       <c r="X23" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Y23" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="AA23" t="n">
@@ -2719,14 +2719,14 @@
         <v>0</v>
       </c>
       <c r="X24" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="Y24" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>25.0%</t>
         </is>
       </c>
       <c r="AA24" t="n">
@@ -3307,14 +3307,14 @@
         <v>0</v>
       </c>
       <c r="X27" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="Y27" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="AA27" t="n">
@@ -3839,14 +3839,14 @@
         <v>0</v>
       </c>
       <c r="X30" t="n">
-        <v>25</v>
+        <v>11</v>
       </c>
       <c r="Y30" t="n">
-        <v>34</v>
+        <v>20</v>
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>73.5%</t>
+          <t>55.0%</t>
         </is>
       </c>
       <c r="AA30" t="n">
@@ -3875,22 +3875,22 @@
         <v>2</v>
       </c>
       <c r="AH30" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AI30" t="inlineStr">
         <is>
-          <t>33.3%</t>
+          <t>28.6%</t>
         </is>
       </c>
       <c r="AJ30" t="n">
         <v>9</v>
       </c>
       <c r="AK30" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AL30" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>52.9%</t>
         </is>
       </c>
       <c r="AM30" t="inlineStr">
@@ -4304,10 +4304,10 @@
         <v>2</v>
       </c>
       <c r="X35" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="Y35" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="Z35" t="inlineStr">
         <is>
@@ -4500,10 +4500,10 @@
         <v>0</v>
       </c>
       <c r="X36" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Y36" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Z36" t="inlineStr">
         <is>
@@ -4696,10 +4696,10 @@
         <v>0</v>
       </c>
       <c r="X37" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="Y37" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="Z37" t="inlineStr">
         <is>
@@ -4732,22 +4732,22 @@
         <v>1</v>
       </c>
       <c r="AH37" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AI37" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>33.3%</t>
         </is>
       </c>
       <c r="AJ37" t="n">
         <v>5</v>
       </c>
       <c r="AK37" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AL37" t="inlineStr">
         <is>
-          <t>62.5%</t>
+          <t>71.4%</t>
         </is>
       </c>
       <c r="AM37" t="inlineStr">
@@ -4892,10 +4892,10 @@
         <v>1</v>
       </c>
       <c r="X38" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="Y38" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="Z38" t="inlineStr">
         <is>
@@ -5088,14 +5088,14 @@
         <v>0</v>
       </c>
       <c r="X39" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="Y39" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>66.7%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="AA39" t="n">
@@ -5480,10 +5480,10 @@
         <v>0</v>
       </c>
       <c r="X41" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="Y41" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="Z41" t="inlineStr">
         <is>
@@ -6460,14 +6460,14 @@
         <v>0</v>
       </c>
       <c r="X46" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="Y46" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="Z46" t="inlineStr">
         <is>
-          <t>85.7%</t>
+          <t>75.0%</t>
         </is>
       </c>
       <c r="AA46" t="n">
@@ -6796,14 +6796,14 @@
         <v>3</v>
       </c>
       <c r="X48" t="n">
-        <v>32</v>
+        <v>14</v>
       </c>
       <c r="Y48" t="n">
-        <v>36</v>
+        <v>18</v>
       </c>
       <c r="Z48" t="inlineStr">
         <is>
-          <t>88.9%</t>
+          <t>77.8%</t>
         </is>
       </c>
       <c r="AA48" t="n">
@@ -6832,22 +6832,22 @@
         <v>3</v>
       </c>
       <c r="AH48" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AI48" t="inlineStr">
         <is>
-          <t>33.3%</t>
+          <t>30.0%</t>
         </is>
       </c>
       <c r="AJ48" t="n">
         <v>6</v>
       </c>
       <c r="AK48" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AL48" t="inlineStr">
         <is>
-          <t>33.3%</t>
+          <t>35.3%</t>
         </is>
       </c>
       <c r="AM48" t="inlineStr">
